--- a/results/job_matches_2026-08-30.xlsx
+++ b/results/job_matches_2026-08-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II, Data (Cloud &amp; AI)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.4</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Databricks, Unity Catalog, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Athena, S3, IAM, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d9b5bcc98f7ba12</t>
+          <t>https://www.indeed.com/viewjob?jk=e3ed8a1f209612e2</t>
         </is>
       </c>
     </row>
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jr DevSecOps Engineer</t>
+          <t>DevOps Platform and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Koniag Government Services</t>
+          <t>Solvonex</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f140f3b3c4a71d9</t>
+          <t>https://www.indeed.com/viewjob?jk=f32791637f5d1fb8</t>
         </is>
       </c>
     </row>
@@ -643,60 +643,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>UNIX MIDDLEWARE ENGINEER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>NYC Human Resources Administration</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, S3, IAM, RDS, Azure, Oracle, SQL Server, ELT, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68b9213bf9a10955</t>
+          <t>https://www.indeed.com/viewjob?jk=3c1fa99b1f49f8e3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77b7eb57f3ad62c6</t>
+          <t>https://www.indeed.com/viewjob?jk=27c60023bc663d82</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27c60023bc663d82</t>
+          <t>https://www.indeed.com/viewjob?jk=4484d09ea245cffb</t>
         </is>
       </c>
     </row>
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4484d09ea245cffb</t>
+          <t>https://www.indeed.com/viewjob?jk=d4dbd28c2635208f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Product Software Engineer II (Java/Full Stack/DevOps)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, S3, SQS, SNS, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4dbd28c2635208f</t>
+          <t>https://www.indeed.com/viewjob?jk=52ac0abbd64d17ed</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UNIX MIDDLEWARE ENGINEER</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NYC Human Resources Administration</t>
+          <t>Department Of Consumer Affairs</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Oracle, SQL Server, ELT, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, MySQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c1fa99b1f49f8e3</t>
+          <t>https://www.indeed.com/viewjob?jk=cd6d29d7f0da02cd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Backend Senior Software Engineer, CX Engineering(Hybrid)</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Kearney, NE, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, NoSQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119b27074f6796ab</t>
+          <t>https://www.indeed.com/viewjob?jk=8ae9405dc478084f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Product Software Engineer II (Java/Full Stack/DevOps)</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52ac0abbd64d17ed</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc099d426154e9c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Associate, Senior Engineer - Institutional Life Technology</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, dbt, CI/CD</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68fedabc5fbe0a42</t>
+          <t>https://www.indeed.com/viewjob?jk=d6982f28b9756d95</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Department Of Consumer Affairs</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, MySQL, MongoDB, ETL</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd6d29d7f0da02cd</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4728d485fd82b7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Grand Island, NE, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, Snowflake, Data Modeling</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad211ca6801fd529</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8a860e6f7c99c7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, Snowflake, Data Modeling</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd833b3f3ca71894</t>
+          <t>https://www.indeed.com/viewjob?jk=4aab656d0ca3d815</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, Snowflake, Data Modeling</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc966b8e4ac5ea90</t>
+          <t>https://www.indeed.com/viewjob?jk=b710a7f0b803f961</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>API Platform Owner</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Axos Bank</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,77 +1116,77 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64225cf49e7ac0e</t>
+          <t>https://www.indeed.com/viewjob?jk=875223ae2058a7a3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Products</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Focus on the Family</t>
+          <t>ron turley associates</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Glendale, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, Time Travel, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, SQS, ECS, RDS, Scala, Kafka, ELT, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b735c1f0f9c927f</t>
+          <t>https://www.indeed.com/viewjob?jk=4875b61328aee0d6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>API Platform Owner</t>
+          <t>Associate, Full Stack Engineer - SMA Solutions</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Axos Bank</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, SQS, RDS, Azure, GCP, SQL Server, PostgreSQL, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875223ae2058a7a3</t>
+          <t>https://www.indeed.com/viewjob?jk=85433a570efd3e4f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Field Specialist - Data Engineering &amp; Streaming (Pre-Sales)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ron turley associates</t>
+          <t>Cloudera</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Glendale, AZ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, RDS, Scala, Kafka, ELT, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Databricks, Dataflow, Spark, Scala, Kafka, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4875b61328aee0d6</t>
+          <t>https://www.indeed.com/viewjob?jk=bf2e066f006a0c05</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Automation Developer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, ELT, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,77 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb32ec10e69dafd1</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Senior Field Specialist - Data Engineering &amp; Streaming (Pre-Sales)</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Cloudera</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, Databricks, Dataflow, Spark, Scala, Kafka, DataOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf2e066f006a0c05</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Associate, Full Stack Engineer - SMA Solutions</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>BlackRock</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, GCP, SQL Server, PostgreSQL, DynamoDB, Cassandra, NoSQL</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=85433a570efd3e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=73756c88cc20b24b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-30.xlsx
+++ b/results/job_matches_2026-08-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,87 +503,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data architect</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, GCP, BigQuery, Spark</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0efe6a35cb61a5</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab555e988dd3c5f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>DevOps Platform and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Solvonex</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab555e988dd3c5f</t>
+          <t>https://www.indeed.com/viewjob?jk=f32791637f5d1fb8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DevOps Platform and Infrastructure Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Solvonex</t>
+          <t>Department of Technology</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,42 +591,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f32791637f5d1fb8</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c6ea2c982d3ce1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
+          <t>Product Software Engineer II (Java/Full Stack/DevOps)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Department of Technology</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, SNS, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c6ea2c982d3ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=52ac0abbd64d17ed</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UNIX MIDDLEWARE ENGINEER</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NYC Human Resources Administration</t>
+          <t>Department Of Consumer Affairs</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Oracle, SQL Server, ELT, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, MySQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,137 +671,137 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c1fa99b1f49f8e3</t>
+          <t>https://www.indeed.com/viewjob?jk=cd6d29d7f0da02cd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kearney, NE, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27c60023bc663d82</t>
+          <t>https://www.indeed.com/viewjob?jk=8ae9405dc478084f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4484d09ea245cffb</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc099d426154e9c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4dbd28c2635208f</t>
+          <t>https://www.indeed.com/viewjob?jk=d6982f28b9756d95</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Product Software Engineer II (Java/Full Stack/DevOps)</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52ac0abbd64d17ed</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4728d485fd82b7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Department Of Consumer Affairs</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Grand Island, NE, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, MySQL, MongoDB, ETL</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd6d29d7f0da02cd</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8a860e6f7c99c7</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kearney, NE, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ae9405dc478084f</t>
+          <t>https://www.indeed.com/viewjob?jk=4aab656d0ca3d815</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc099d426154e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=b710a7f0b803f961</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>API Platform Owner</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Axos Bank</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6982f28b9756d95</t>
+          <t>https://www.indeed.com/viewjob?jk=875223ae2058a7a3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>ron turley associates</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Glendale, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, ECS, RDS, Scala, Kafka, ELT, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4728d485fd82b7</t>
+          <t>https://www.indeed.com/viewjob?jk=4875b61328aee0d6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Associate, Full Stack Engineer - SMA Solutions</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Grand Island, NE, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, GCP, SQL Server, PostgreSQL, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8a860e6f7c99c7</t>
+          <t>https://www.indeed.com/viewjob?jk=85433a570efd3e4f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1055,216 +1055,6 @@
         </is>
       </c>
       <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4aab656d0ca3d815</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ALLO Communications</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b710a7f0b803f961</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>API Platform Owner</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Axos Bank</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=875223ae2058a7a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ron turley associates</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Glendale, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AWS, SQS, ECS, RDS, Scala, Kafka, ELT, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4875b61328aee0d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Associate, Full Stack Engineer - SMA Solutions</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>BlackRock</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, GCP, SQL Server, PostgreSQL, DynamoDB, Cassandra, NoSQL</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=85433a570efd3e4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Senior Field Specialist - Data Engineering &amp; Streaming (Pre-Sales)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Cloudera</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, Databricks, Dataflow, Spark, Scala, Kafka, DataOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf2e066f006a0c05</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>RBC</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=73756c88cc20b24b</t>
         </is>

--- a/results/job_matches_2026-08-30.xlsx
+++ b/results/job_matches_2026-08-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Department of Technology</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Kearney, NE, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c6ea2c982d3ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=8ae9405dc478084f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Product Software Engineer II (Java/Full Stack/DevOps)</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52ac0abbd64d17ed</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc099d426154e9c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Department Of Consumer Affairs</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, MySQL, MongoDB, ETL</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd6d29d7f0da02cd</t>
+          <t>https://www.indeed.com/viewjob?jk=d6982f28b9756d95</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kearney, NE, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ae9405dc478084f</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4728d485fd82b7</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Grand Island, NE, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc099d426154e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8a860e6f7c99c7</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6982f28b9756d95</t>
+          <t>https://www.indeed.com/viewjob?jk=4aab656d0ca3d815</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4728d485fd82b7</t>
+          <t>https://www.indeed.com/viewjob?jk=b710a7f0b803f961</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Grand Island, NE, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8a860e6f7c99c7</t>
+          <t>https://www.indeed.com/viewjob?jk=c9493a61af734ed1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>ron turley associates</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Glendale, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, ECS, RDS, Scala, Kafka, ELT, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aab656d0ca3d815</t>
+          <t>https://www.indeed.com/viewjob?jk=4875b61328aee0d6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -915,146 +915,6 @@
         </is>
       </c>
       <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b710a7f0b803f961</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>API Platform Owner</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Axos Bank</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=875223ae2058a7a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>ron turley associates</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Glendale, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AWS, SQS, ECS, RDS, Scala, Kafka, ELT, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4875b61328aee0d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Associate, Full Stack Engineer - SMA Solutions</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>BlackRock</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, GCP, SQL Server, PostgreSQL, DynamoDB, Cassandra, NoSQL</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=85433a570efd3e4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>RBC</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=73756c88cc20b24b</t>
         </is>

--- a/results/job_matches_2026-08-30.xlsx
+++ b/results/job_matches_2026-08-30.xlsx
@@ -573,35 +573,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>AIPowered Power BI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kearney, NE, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ae9405dc478084f</t>
+          <t>https://www.indeed.com/viewjob?jk=5865f55ab1e5c5e9</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Kearney, NE, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc099d426154e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=8ae9405dc478084f</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6982f28b9756d95</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc099d426154e9c</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4728d485fd82b7</t>
+          <t>https://www.indeed.com/viewjob?jk=d6982f28b9756d95</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Grand Island, NE, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8a860e6f7c99c7</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4728d485fd82b7</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Grand Island, NE, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aab656d0ca3d815</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8a860e6f7c99c7</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b710a7f0b803f961</t>
+          <t>https://www.indeed.com/viewjob?jk=4aab656d0ca3d815</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9493a61af734ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=b710a7f0b803f961</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ron turley associates</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Glendale, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, RDS, Scala, Kafka, ELT, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4875b61328aee0d6</t>
+          <t>https://www.indeed.com/viewjob?jk=c9493a61af734ed1</t>
         </is>
       </c>
     </row>
